--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.beta.natif/Resultats_ratio.beta.natif_moy_RMSEP.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.beta.natif/Resultats_ratio.beta.natif_moy_RMSEP.xlsx
@@ -1,211 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\ratio.beta.natif\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>RMSEP_glo</t>
-  </si>
-  <si>
-    <t>LV0_RMSEP</t>
-  </si>
-  <si>
-    <t>LV1_RMSEP</t>
-  </si>
-  <si>
-    <t>LV2_RMSEP</t>
-  </si>
-  <si>
-    <t>LV3_RMSEP</t>
-  </si>
-  <si>
-    <t>LV4_RMSEP</t>
-  </si>
-  <si>
-    <t>LV5_RMSEP</t>
-  </si>
-  <si>
-    <t>LV6_RMSEP</t>
-  </si>
-  <si>
-    <t>LV7_RMSEP</t>
-  </si>
-  <si>
-    <t>LV8_RMSEP</t>
-  </si>
-  <si>
-    <t>LV9_RMSEP</t>
-  </si>
-  <si>
-    <t>LV10_RMSEP</t>
-  </si>
-  <si>
-    <t>LV11_RMSEP</t>
-  </si>
-  <si>
-    <t>LV12_RMSEP</t>
-  </si>
-  <si>
-    <t>LV13_RMSEP</t>
-  </si>
-  <si>
-    <t>LV14_RMSEP</t>
-  </si>
-  <si>
-    <t>LV15_RMSEP</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -253,19 +63,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -307,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -339,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -374,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -550,2436 +350,2539 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RMSEP_glo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_RMSEP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_RMSEP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_RMSEP</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_RMSEP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_RMSEP</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_RMSEP</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_RMSEP</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_RMSEP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_RMSEP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_RMSEP</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_RMSEP</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_RMSEP</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_RMSEP</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_RMSEP</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_RMSEP</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_RMSEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>0.10042155466782229</v>
+        <v>0.1004215589400185</v>
       </c>
       <c r="C2">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D2">
-        <v>0.11484108298228091</v>
+        <v>0.1148410889021708</v>
       </c>
       <c r="E2">
-        <v>0.11724876855100951</v>
+        <v>0.1172487763500216</v>
       </c>
       <c r="F2">
-        <v>0.1168044690109581</v>
+        <v>0.1168044765712413</v>
       </c>
       <c r="G2">
-        <v>0.11573611568839939</v>
+        <v>0.1157361206615441</v>
       </c>
       <c r="H2">
-        <v>0.11698765909947451</v>
+        <v>0.1169876707835956</v>
       </c>
       <c r="I2">
-        <v>0.1168909907370468</v>
+        <v>0.1168909987960978</v>
       </c>
       <c r="J2">
-        <v>0.1136493638034104</v>
+        <v>0.1136493695879464</v>
       </c>
       <c r="K2">
-        <v>0.11052387995498859</v>
+        <v>0.1105238854390095</v>
       </c>
       <c r="L2">
-        <v>0.1120788649414871</v>
+        <v>0.1120788702143962</v>
       </c>
       <c r="M2">
-        <v>0.1095974115368132</v>
+        <v>0.1095974174343119</v>
       </c>
       <c r="N2">
-        <v>0.1048061649332418</v>
+        <v>0.1048061696337741</v>
       </c>
       <c r="O2">
-        <v>0.10330370330220991</v>
+        <v>0.1033037090416359</v>
       </c>
       <c r="P2">
-        <v>9.6770166528576923E-2</v>
+        <v>0.09677017218393542</v>
       </c>
       <c r="Q2">
-        <v>9.0623601421005021E-2</v>
+        <v>0.0906236048794473</v>
       </c>
       <c r="R2">
-        <v>8.7997932286218411E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>19</v>
+        <v>0.08799793652804168</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>0.1049236330943176</v>
+        <v>0.1049236575299308</v>
       </c>
       <c r="C3">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D3">
-        <v>0.1133398249411089</v>
+        <v>0.1133398311908712</v>
       </c>
       <c r="E3">
-        <v>0.12300763422809601</v>
+        <v>0.1230076444071812</v>
       </c>
       <c r="F3">
-        <v>0.1196634870401594</v>
+        <v>0.1196634946277961</v>
       </c>
       <c r="G3">
-        <v>0.11140821303327859</v>
+        <v>0.1114082238415474</v>
       </c>
       <c r="H3">
-        <v>0.106224048194899</v>
+        <v>0.1062240547779136</v>
       </c>
       <c r="I3">
-        <v>0.10332345569424969</v>
+        <v>0.1033234689989363</v>
       </c>
       <c r="J3">
-        <v>9.9820884347234351E-2</v>
+        <v>0.09982090180202884</v>
       </c>
       <c r="K3">
-        <v>9.7957666655196243E-2</v>
+        <v>0.09795766785114671</v>
       </c>
       <c r="L3">
-        <v>9.4872972318038928E-2</v>
+        <v>0.09487297391811583</v>
       </c>
       <c r="M3">
-        <v>9.2931433396290702E-2</v>
+        <v>0.09293143327447831</v>
       </c>
       <c r="N3">
-        <v>9.3460692518769845E-2</v>
+        <v>0.09346069076280648</v>
       </c>
       <c r="O3">
-        <v>9.3904018255557359E-2</v>
+        <v>0.09390401278548133</v>
       </c>
       <c r="P3">
-        <v>9.5337465209923214E-2</v>
+        <v>0.09533745221685605</v>
       </c>
       <c r="Q3">
-        <v>9.6337981897531136E-2</v>
+        <v>0.09633797313697899</v>
       </c>
       <c r="R3">
-        <v>9.4931751009276588E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>20</v>
+        <v>0.09493170000314341</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>0.1086824012916955</v>
+        <v>0.1086824047065331</v>
       </c>
       <c r="C4">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D4">
-        <v>0.1144500091021714</v>
+        <v>0.1144500151669839</v>
       </c>
       <c r="E4">
-        <v>0.1156640107733545</v>
+        <v>0.115664017619498</v>
       </c>
       <c r="F4">
-        <v>0.1195751674801086</v>
+        <v>0.1195751747270651</v>
       </c>
       <c r="G4">
-        <v>0.120012703058266</v>
+        <v>0.1200127110260279</v>
       </c>
       <c r="H4">
-        <v>0.1230883008176038</v>
+        <v>0.1230883060720872</v>
       </c>
       <c r="I4">
-        <v>0.1163785161806828</v>
+        <v>0.1163785204526529</v>
       </c>
       <c r="J4">
-        <v>0.11188613585363449</v>
+        <v>0.1118861419170329</v>
       </c>
       <c r="K4">
-        <v>0.109321581508787</v>
+        <v>0.1093215871281468</v>
       </c>
       <c r="L4">
-        <v>0.1087070065833733</v>
+        <v>0.1087070088569152</v>
       </c>
       <c r="M4">
-        <v>0.10466438214059059</v>
+        <v>0.1046643875465481</v>
       </c>
       <c r="N4">
-        <v>0.1000562579620811</v>
+        <v>0.1000562615418077</v>
       </c>
       <c r="O4">
-        <v>9.6309745465086041E-2</v>
+        <v>0.09630974873395047</v>
       </c>
       <c r="P4">
-        <v>9.3958124516427904E-2</v>
+        <v>0.09395812807517918</v>
       </c>
       <c r="Q4">
-        <v>9.3897585513068871E-2</v>
+        <v>0.09389758931053165</v>
       </c>
       <c r="R4">
-        <v>9.4981676984736044E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>21</v>
+        <v>0.09498168081496676</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>9.7454870012573844E-2</v>
+        <v>0.09745487477143475</v>
       </c>
       <c r="C5">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D5">
-        <v>0.1139449002160591</v>
+        <v>0.1139449065409995</v>
       </c>
       <c r="E5">
-        <v>0.117575797133684</v>
+        <v>0.1175758052085376</v>
       </c>
       <c r="F5">
-        <v>0.1148997548091346</v>
+        <v>0.1148997597726284</v>
       </c>
       <c r="G5">
-        <v>0.1198370462403502</v>
+        <v>0.1198370514901624</v>
       </c>
       <c r="H5">
-        <v>0.1092826573667199</v>
+        <v>0.1092826636558899</v>
       </c>
       <c r="I5">
-        <v>0.1040377515939412</v>
+        <v>0.1040377566821821</v>
       </c>
       <c r="J5">
-        <v>0.10125688974330101</v>
+        <v>0.1012568939724916</v>
       </c>
       <c r="K5">
-        <v>9.6705727373325903E-2</v>
+        <v>0.09670573316632766</v>
       </c>
       <c r="L5">
-        <v>9.1890001675358254E-2</v>
+        <v>0.09189000381951103</v>
       </c>
       <c r="M5">
-        <v>8.9917617731852487E-2</v>
+        <v>0.08991761695985175</v>
       </c>
       <c r="N5">
-        <v>8.771408672123375E-2</v>
+        <v>0.08771408563544109</v>
       </c>
       <c r="O5">
-        <v>8.7580398047972116E-2</v>
+        <v>0.08758039566483801</v>
       </c>
       <c r="P5">
-        <v>8.9431784850402707E-2</v>
+        <v>0.08943178109413139</v>
       </c>
       <c r="Q5">
-        <v>9.0575984371270415E-2</v>
+        <v>0.09057597823276071</v>
       </c>
       <c r="R5">
-        <v>9.2280463374823235E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>22</v>
+        <v>0.09228045515540947</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>9.4657166256619962E-2</v>
+        <v>0.09465718821591981</v>
       </c>
       <c r="C6">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D6">
-        <v>0.11405518313136991</v>
+        <v>0.1140551891746732</v>
       </c>
       <c r="E6">
-        <v>0.1188971406618423</v>
+        <v>0.1188971497727761</v>
       </c>
       <c r="F6">
-        <v>0.116364387223456</v>
+        <v>0.1163643943705811</v>
       </c>
       <c r="G6">
-        <v>0.1180791143418659</v>
+        <v>0.1180791191416897</v>
       </c>
       <c r="H6">
-        <v>0.1057425307156427</v>
+        <v>0.1057424987569237</v>
       </c>
       <c r="I6">
-        <v>9.9460182058731542E-2</v>
+        <v>0.09946052391463607</v>
       </c>
       <c r="J6">
-        <v>9.6085245585163084E-2</v>
+        <v>0.09608526499385342</v>
       </c>
       <c r="K6">
-        <v>9.0578905325327808E-2</v>
+        <v>0.09057890930640282</v>
       </c>
       <c r="L6">
-        <v>8.7856955532271297E-2</v>
+        <v>0.08785697275773252</v>
       </c>
       <c r="M6">
-        <v>8.7078461890235256E-2</v>
+        <v>0.08707847297838628</v>
       </c>
       <c r="N6">
-        <v>8.5591172214724814E-2</v>
+        <v>0.08559117560623879</v>
       </c>
       <c r="O6">
-        <v>8.5081123001868597E-2</v>
+        <v>0.08508112593489994</v>
       </c>
       <c r="P6">
-        <v>8.5854671101381924E-2</v>
+        <v>0.08585467337379485</v>
       </c>
       <c r="Q6">
-        <v>8.5357327405283595E-2</v>
+        <v>0.08535732822895904</v>
       </c>
       <c r="R6">
-        <v>8.6939855015819217E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
+        <v>0.08693985808950781</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>0.10610403784969639</v>
+        <v>0.1061040371221418</v>
       </c>
       <c r="C7">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D7">
-        <v>0.1144962419327282</v>
+        <v>0.1144962477300786</v>
       </c>
       <c r="E7">
-        <v>0.1157670103724374</v>
+        <v>0.1157670181244922</v>
       </c>
       <c r="F7">
-        <v>0.1193677731041393</v>
+        <v>0.1193677782783576</v>
       </c>
       <c r="G7">
-        <v>0.1206275461530391</v>
+        <v>0.1206275506027691</v>
       </c>
       <c r="H7">
-        <v>0.12423887743746009</v>
+        <v>0.1242388844009833</v>
       </c>
       <c r="I7">
-        <v>0.12138098248148731</v>
+        <v>0.1213809858660653</v>
       </c>
       <c r="J7">
-        <v>0.1154992983915641</v>
+        <v>0.1154993038149698</v>
       </c>
       <c r="K7">
-        <v>0.1100747780105093</v>
+        <v>0.1100747789022828</v>
       </c>
       <c r="L7">
-        <v>0.1085497832628402</v>
+        <v>0.1085497851746093</v>
       </c>
       <c r="M7">
-        <v>0.1077991316773543</v>
+        <v>0.1077991324191388</v>
       </c>
       <c r="N7">
-        <v>0.1014971063465777</v>
+        <v>0.1014971088187181</v>
       </c>
       <c r="O7">
-        <v>9.6999284414264669E-2</v>
+        <v>0.09699928828313688</v>
       </c>
       <c r="P7">
-        <v>9.321038057818358E-2</v>
+        <v>0.09321042930183236</v>
       </c>
       <c r="Q7">
-        <v>9.1639386975408091E-2</v>
+        <v>0.09163939149874439</v>
       </c>
       <c r="R7">
-        <v>9.135982499410443E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>24</v>
+        <v>0.091359829084406</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>0.10166208199045949</v>
+        <v>0.1016620851579859</v>
       </c>
       <c r="C8">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D8">
-        <v>0.1143002829336638</v>
+        <v>0.1143002888673802</v>
       </c>
       <c r="E8">
-        <v>0.11596736453590049</v>
+        <v>0.1159673711237715</v>
       </c>
       <c r="F8">
-        <v>0.1198213405870186</v>
+        <v>0.1198213492108425</v>
       </c>
       <c r="G8">
-        <v>0.1223796919127469</v>
+        <v>0.1223796960693602</v>
       </c>
       <c r="H8">
-        <v>0.1188043765115096</v>
+        <v>0.1188043817923743</v>
       </c>
       <c r="I8">
-        <v>0.1129748587966032</v>
+        <v>0.1129748644893009</v>
       </c>
       <c r="J8">
-        <v>0.1120276568542295</v>
+        <v>0.112027664362921</v>
       </c>
       <c r="K8">
-        <v>0.1059902726669332</v>
+        <v>0.1059902752101042</v>
       </c>
       <c r="L8">
-        <v>0.1032553697056524</v>
+        <v>0.1032553728939155</v>
       </c>
       <c r="M8">
-        <v>9.596342650670843E-2</v>
+        <v>0.09596343009910713</v>
       </c>
       <c r="N8">
-        <v>9.4841323617117612E-2</v>
+        <v>0.09484132812068466</v>
       </c>
       <c r="O8">
-        <v>9.2035935131598037E-2</v>
+        <v>0.09203593392022807</v>
       </c>
       <c r="P8">
-        <v>9.0366169698863852E-2</v>
+        <v>0.09036616982487761</v>
       </c>
       <c r="Q8">
-        <v>9.039175894888403E-2</v>
+        <v>0.09039176359146435</v>
       </c>
       <c r="R8">
-        <v>9.122571097172999E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>25</v>
+        <v>0.09122571503694112</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>9.8235914835941615E-2</v>
+        <v>0.09823591937224448</v>
       </c>
       <c r="C9">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D9">
-        <v>0.11411639661733521</v>
+        <v>0.1141164025302845</v>
       </c>
       <c r="E9">
-        <v>0.1154128155202583</v>
+        <v>0.115412822294863</v>
       </c>
       <c r="F9">
-        <v>0.1190387391063658</v>
+        <v>0.1190387480057704</v>
       </c>
       <c r="G9">
-        <v>0.120654580389187</v>
+        <v>0.1206545843610747</v>
       </c>
       <c r="H9">
-        <v>0.1180242811916562</v>
+        <v>0.1180242874300986</v>
       </c>
       <c r="I9">
-        <v>0.1123521177473417</v>
+        <v>0.1123521223135611</v>
       </c>
       <c r="J9">
-        <v>0.111678235876799</v>
+        <v>0.1116782376278382</v>
       </c>
       <c r="K9">
-        <v>0.1058723264493525</v>
+        <v>0.1058723284169941</v>
       </c>
       <c r="L9">
-        <v>0.1040930828560801</v>
+        <v>0.1040930945106742</v>
       </c>
       <c r="M9">
-        <v>9.4302858931938807E-2</v>
+        <v>0.0943028636440971</v>
       </c>
       <c r="N9">
-        <v>9.483776903281553E-2</v>
+        <v>0.09483777352228505</v>
       </c>
       <c r="O9">
-        <v>9.175947879894579E-2</v>
+        <v>0.09175948304753813</v>
       </c>
       <c r="P9">
-        <v>8.9812415878787744E-2</v>
+        <v>0.0898124207807479</v>
       </c>
       <c r="Q9">
-        <v>9.0087417861404007E-2</v>
+        <v>0.0900874225966386</v>
       </c>
       <c r="R9">
-        <v>9.0212072387738221E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>26</v>
+        <v>0.09021207871390678</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>9.9698459232406278E-2</v>
+        <v>0.09969846309085348</v>
       </c>
       <c r="C10">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D10">
-        <v>0.1142534587394905</v>
+        <v>0.1142534646315193</v>
       </c>
       <c r="E10">
-        <v>0.1159564535864604</v>
+        <v>0.1159564624649923</v>
       </c>
       <c r="F10">
-        <v>0.1194475039821329</v>
+        <v>0.1194475102621088</v>
       </c>
       <c r="G10">
-        <v>0.12079692872941609</v>
+        <v>0.1207969322124745</v>
       </c>
       <c r="H10">
-        <v>0.11809365172186061</v>
+        <v>0.1180936567481448</v>
       </c>
       <c r="I10">
-        <v>0.11226240817421219</v>
+        <v>0.1122624130337163</v>
       </c>
       <c r="J10">
-        <v>0.1115156119120297</v>
+        <v>0.1115156142742184</v>
       </c>
       <c r="K10">
-        <v>0.1057761125139767</v>
+        <v>0.1057761141843581</v>
       </c>
       <c r="L10">
-        <v>0.1036696665306121</v>
+        <v>0.103669667835639</v>
       </c>
       <c r="M10">
-        <v>9.4219295353785038E-2</v>
+        <v>0.09421929985751322</v>
       </c>
       <c r="N10">
-        <v>9.5026952018054042E-2</v>
+        <v>0.09502696220107418</v>
       </c>
       <c r="O10">
-        <v>9.2093674226497418E-2</v>
+        <v>0.09209368164570508</v>
       </c>
       <c r="P10">
-        <v>9.0280558186657381E-2</v>
+        <v>0.09028056319134764</v>
       </c>
       <c r="Q10">
-        <v>9.087411621643543E-2</v>
+        <v>0.09087412163617341</v>
       </c>
       <c r="R10">
-        <v>9.1178074837877127E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>27</v>
+        <v>0.09117808521084125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>9.9404661993708079E-2</v>
+        <v>0.09940466609369028</v>
       </c>
       <c r="C11">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D11">
-        <v>0.1140840451259349</v>
+        <v>0.1140840511203362</v>
       </c>
       <c r="E11">
-        <v>0.1157009861247254</v>
+        <v>0.1157009948170803</v>
       </c>
       <c r="F11">
-        <v>0.1192177622046232</v>
+        <v>0.1192177682491713</v>
       </c>
       <c r="G11">
-        <v>0.1208178538479093</v>
+        <v>0.1208179151552166</v>
       </c>
       <c r="H11">
-        <v>0.1181632298772354</v>
+        <v>0.1181632443060745</v>
       </c>
       <c r="I11">
-        <v>0.1125019846049834</v>
+        <v>0.11250198927888</v>
       </c>
       <c r="J11">
-        <v>0.11212909575642439</v>
+        <v>0.1121291015819593</v>
       </c>
       <c r="K11">
-        <v>0.1064306745123679</v>
+        <v>0.1064306780372806</v>
       </c>
       <c r="L11">
-        <v>0.1048588097740412</v>
+        <v>0.1048588156274718</v>
       </c>
       <c r="M11">
-        <v>9.5107174200207631E-2</v>
+        <v>0.09510717796688564</v>
       </c>
       <c r="N11">
-        <v>9.4883494441357338E-2</v>
+        <v>0.09488349880702553</v>
       </c>
       <c r="O11">
-        <v>9.1768210985464102E-2</v>
+        <v>0.09176821509447253</v>
       </c>
       <c r="P11">
-        <v>8.981082295489437E-2</v>
+        <v>0.0898108273649155</v>
       </c>
       <c r="Q11">
-        <v>9.0316433317744457E-2</v>
+        <v>0.09031643827409268</v>
       </c>
       <c r="R11">
-        <v>9.0377229342008827E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>28</v>
+        <v>0.09037723474095909</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>9.3199153917695718E-2</v>
+        <v>0.09319915690256507</v>
       </c>
       <c r="C12">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D12">
-        <v>0.1136448477983663</v>
+        <v>0.1136448538791311</v>
       </c>
       <c r="E12">
-        <v>0.1172949624909152</v>
+        <v>0.1172949705046498</v>
       </c>
       <c r="F12">
-        <v>0.11525066223277459</v>
+        <v>0.1152506676750722</v>
       </c>
       <c r="G12">
-        <v>0.12003393681072989</v>
+        <v>0.1200339413256369</v>
       </c>
       <c r="H12">
-        <v>0.10963976675229339</v>
+        <v>0.1096397742219993</v>
       </c>
       <c r="I12">
-        <v>0.1064724534150378</v>
+        <v>0.1064724611540664</v>
       </c>
       <c r="J12">
-        <v>9.9304450561336799E-2</v>
+        <v>0.09930445419206863</v>
       </c>
       <c r="K12">
-        <v>9.2867336725150226E-2</v>
+        <v>0.09286734058636424</v>
       </c>
       <c r="L12">
-        <v>8.8821699499248633E-2</v>
+        <v>0.08882169997593314</v>
       </c>
       <c r="M12">
-        <v>8.6914399423174762E-2</v>
+        <v>0.08691439955170729</v>
       </c>
       <c r="N12">
-        <v>8.4877461223337586E-2</v>
+        <v>0.08487745954711401</v>
       </c>
       <c r="O12">
-        <v>8.4663468961460292E-2</v>
+        <v>0.08466346612580082</v>
       </c>
       <c r="P12">
-        <v>8.6380865322010919E-2</v>
+        <v>0.08638086152303008</v>
       </c>
       <c r="Q12">
-        <v>8.8171534124818624E-2</v>
+        <v>0.08817152934184971</v>
       </c>
       <c r="R12">
-        <v>9.141668267477468E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>29</v>
+        <v>0.09141667511470361</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>0.10974047750175921</v>
+        <v>0.1097404801913978</v>
       </c>
       <c r="C13">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D13">
-        <v>0.1144123719477297</v>
+        <v>0.1144123790988669</v>
       </c>
       <c r="E13">
-        <v>0.1219445040754232</v>
+        <v>0.1219445113375562</v>
       </c>
       <c r="F13">
-        <v>0.118399295233555</v>
+        <v>0.1183992993658386</v>
       </c>
       <c r="G13">
-        <v>0.1211341747493207</v>
+        <v>0.1211341838149152</v>
       </c>
       <c r="H13">
-        <v>0.1206167732569472</v>
+        <v>0.1206167799985583</v>
       </c>
       <c r="I13">
-        <v>0.1124766693992077</v>
+        <v>0.112476693702141</v>
       </c>
       <c r="J13">
-        <v>0.1123611892064023</v>
+        <v>0.1123607488776235</v>
       </c>
       <c r="K13">
-        <v>0.1095177727199316</v>
+        <v>0.1095167105939608</v>
       </c>
       <c r="L13">
-        <v>0.1045580728143862</v>
+        <v>0.1045581253162426</v>
       </c>
       <c r="M13">
-        <v>9.9859599512187022E-2</v>
+        <v>0.09985959998820221</v>
       </c>
       <c r="N13">
-        <v>9.9112403743264077E-2</v>
+        <v>0.0991124056383067</v>
       </c>
       <c r="O13">
-        <v>9.6936088175688911E-2</v>
+        <v>0.09693609029741666</v>
       </c>
       <c r="P13">
-        <v>9.6908434637691068E-2</v>
+        <v>0.09690843443918309</v>
       </c>
       <c r="Q13">
-        <v>9.5674294533854704E-2</v>
+        <v>0.09567429143554484</v>
       </c>
       <c r="R13">
-        <v>9.6529771499738487E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
+        <v>0.09652976453924927</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>9.7700224233111546E-2</v>
+        <v>0.09770022238688027</v>
       </c>
       <c r="C14">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D14">
-        <v>0.1146224595736311</v>
+        <v>0.1146224655552161</v>
       </c>
       <c r="E14">
-        <v>0.1158347931843534</v>
+        <v>0.1158347992533708</v>
       </c>
       <c r="F14">
-        <v>0.1193149033492112</v>
+        <v>0.1193149039940477</v>
       </c>
       <c r="G14">
-        <v>0.11998830085816881</v>
+        <v>0.119988312534841</v>
       </c>
       <c r="H14">
-        <v>0.1231604069719173</v>
+        <v>0.1231604228131351</v>
       </c>
       <c r="I14">
-        <v>0.1211442643680388</v>
+        <v>0.1211442666755458</v>
       </c>
       <c r="J14">
-        <v>0.11523622189070749</v>
+        <v>0.1152362277262348</v>
       </c>
       <c r="K14">
-        <v>0.1099520222251079</v>
+        <v>0.1099520262707414</v>
       </c>
       <c r="L14">
-        <v>0.10817917436836461</v>
+        <v>0.1081791789839268</v>
       </c>
       <c r="M14">
-        <v>0.10749142188831901</v>
+        <v>0.1074914247346579</v>
       </c>
       <c r="N14">
-        <v>0.10089296952995409</v>
+        <v>0.1008929764462415</v>
       </c>
       <c r="O14">
-        <v>9.3666417404582564E-2</v>
+        <v>0.09366642020215071</v>
       </c>
       <c r="P14">
-        <v>9.077710423743332E-2</v>
+        <v>0.09077710188372537</v>
       </c>
       <c r="Q14">
-        <v>8.8909500939559086E-2</v>
+        <v>0.08890950602904164</v>
       </c>
       <c r="R14">
-        <v>8.7821991168907459E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>31</v>
+        <v>0.08782199640600948</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>0.10314912552583751</v>
+        <v>0.1031491302971969</v>
       </c>
       <c r="C15">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D15">
-        <v>0.1147003384509484</v>
+        <v>0.1147003443439581</v>
       </c>
       <c r="E15">
-        <v>0.1158326044294726</v>
+        <v>0.1158326122299872</v>
       </c>
       <c r="F15">
-        <v>0.1193784110528201</v>
+        <v>0.1193784183032706</v>
       </c>
       <c r="G15">
-        <v>0.1203338818756869</v>
+        <v>0.1203338875250672</v>
       </c>
       <c r="H15">
-        <v>0.12354985572639671</v>
+        <v>0.1235498605192545</v>
       </c>
       <c r="I15">
-        <v>0.1210310380404237</v>
+        <v>0.1210310421323823</v>
       </c>
       <c r="J15">
-        <v>0.1153851418683528</v>
+        <v>0.1153851467938998</v>
       </c>
       <c r="K15">
-        <v>0.11052476192600851</v>
+        <v>0.1105247690816846</v>
       </c>
       <c r="L15">
-        <v>0.1093130002007789</v>
+        <v>0.1093130054629014</v>
       </c>
       <c r="M15">
-        <v>0.108272471456017</v>
+        <v>0.1082724789315958</v>
       </c>
       <c r="N15">
-        <v>0.1024715718612156</v>
+        <v>0.1024715735693711</v>
       </c>
       <c r="O15">
-        <v>9.6409310726543254E-2</v>
+        <v>0.09640931521296209</v>
       </c>
       <c r="P15">
-        <v>9.3657531948789494E-2</v>
+        <v>0.09365753656038049</v>
       </c>
       <c r="Q15">
-        <v>9.184176961733323E-2</v>
+        <v>0.09184177431990526</v>
       </c>
       <c r="R15">
-        <v>9.0611145097549736E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>32</v>
+        <v>0.09061114991641167</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>0.1024712884284865</v>
+        <v>0.1024712938583986</v>
       </c>
       <c r="C16">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D16">
-        <v>0.1143425285121223</v>
+        <v>0.1143425344660458</v>
       </c>
       <c r="E16">
-        <v>0.1155832477061334</v>
+        <v>0.1155832549238298</v>
       </c>
       <c r="F16">
-        <v>0.11934192532477431</v>
+        <v>0.1193419318106943</v>
       </c>
       <c r="G16">
-        <v>0.1204025645379638</v>
+        <v>0.1204025728972069</v>
       </c>
       <c r="H16">
-        <v>0.123497320283627</v>
+        <v>0.1234973328076498</v>
       </c>
       <c r="I16">
-        <v>0.1215766848053576</v>
+        <v>0.1215767088553501</v>
       </c>
       <c r="J16">
-        <v>0.1158584679550085</v>
+        <v>0.1158584721975253</v>
       </c>
       <c r="K16">
-        <v>0.11120004787059901</v>
+        <v>0.1112000517287852</v>
       </c>
       <c r="L16">
-        <v>0.10963941547983</v>
+        <v>0.1096394215229878</v>
       </c>
       <c r="M16">
-        <v>0.1088836727094081</v>
+        <v>0.1088836826096301</v>
       </c>
       <c r="N16">
-        <v>0.1034168279880618</v>
+        <v>0.1034168337308715</v>
       </c>
       <c r="O16">
-        <v>9.6087805997768505E-2</v>
+        <v>0.096087812468515</v>
       </c>
       <c r="P16">
-        <v>9.3635203930024113E-2</v>
+        <v>0.09363520854648903</v>
       </c>
       <c r="Q16">
-        <v>9.1640150230205594E-2</v>
+        <v>0.09164015520036875</v>
       </c>
       <c r="R16">
-        <v>8.9834419317742914E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>33</v>
+        <v>0.08983442496911002</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>0.106725392999478</v>
+        <v>0.1067253974842728</v>
       </c>
       <c r="C17">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D17">
-        <v>0.11456481107047441</v>
+        <v>0.1145648169447645</v>
       </c>
       <c r="E17">
-        <v>0.1158703268492646</v>
+        <v>0.115870333541456</v>
       </c>
       <c r="F17">
-        <v>0.1193784978924543</v>
+        <v>0.1193785040962405</v>
       </c>
       <c r="G17">
-        <v>0.120249586430224</v>
+        <v>0.1202495952183101</v>
       </c>
       <c r="H17">
-        <v>0.1234484202137358</v>
+        <v>0.1234484271323659</v>
       </c>
       <c r="I17">
-        <v>0.12128877888282411</v>
+        <v>0.12128879636418</v>
       </c>
       <c r="J17">
-        <v>0.1156737647395729</v>
+        <v>0.1156737702433038</v>
       </c>
       <c r="K17">
-        <v>0.1112251743338853</v>
+        <v>0.1112251899227584</v>
       </c>
       <c r="L17">
-        <v>0.1100668177894599</v>
+        <v>0.1100668232036423</v>
       </c>
       <c r="M17">
-        <v>0.10921578392780611</v>
+        <v>0.1092157883930857</v>
       </c>
       <c r="N17">
-        <v>0.10371084271647681</v>
+        <v>0.1037108608640215</v>
       </c>
       <c r="O17">
-        <v>9.7665972301395038E-2</v>
+        <v>0.09766597817905835</v>
       </c>
       <c r="P17">
-        <v>9.5422472591888033E-2</v>
+        <v>0.09542247712817474</v>
       </c>
       <c r="Q17">
-        <v>9.3541474688390885E-2</v>
+        <v>0.09354147890587357</v>
       </c>
       <c r="R17">
-        <v>9.1805711756656486E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>34</v>
+        <v>0.09180571696546724</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>9.3688810471094841E-2</v>
+        <v>0.09368881271752043</v>
       </c>
       <c r="C18">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D18">
-        <v>0.11393013322163351</v>
+        <v>0.1139301398143985</v>
       </c>
       <c r="E18">
-        <v>0.1178219777346828</v>
+        <v>0.1178219856710747</v>
       </c>
       <c r="F18">
-        <v>0.11579097691064751</v>
+        <v>0.1157909819632953</v>
       </c>
       <c r="G18">
-        <v>0.1207096478478861</v>
+        <v>0.1207096625484981</v>
       </c>
       <c r="H18">
-        <v>0.10895661903966811</v>
+        <v>0.1089566512362719</v>
       </c>
       <c r="I18">
-        <v>0.10430804540949221</v>
+        <v>0.1043080512574376</v>
       </c>
       <c r="J18">
-        <v>9.9902918614680661E-2</v>
+        <v>0.09990292344520205</v>
       </c>
       <c r="K18">
-        <v>9.3859790676440069E-2</v>
+        <v>0.09385979381556639</v>
       </c>
       <c r="L18">
-        <v>8.8944209188767276E-2</v>
+        <v>0.08894421315236624</v>
       </c>
       <c r="M18">
-        <v>8.7761069722490592E-2</v>
+        <v>0.08776106605207447</v>
       </c>
       <c r="N18">
-        <v>8.573550400489964E-2</v>
+        <v>0.08573550274351566</v>
       </c>
       <c r="O18">
-        <v>8.5716114460570952E-2</v>
+        <v>0.0857161123123532</v>
       </c>
       <c r="P18">
-        <v>8.7325087901243659E-2</v>
+        <v>0.0873250845075393</v>
       </c>
       <c r="Q18">
-        <v>8.9330252048484077E-2</v>
+        <v>0.08933024725126729</v>
       </c>
       <c r="R18">
-        <v>9.0497447488615296E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>35</v>
+        <v>0.09049744030202742</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>9.2838027015925709E-2</v>
+        <v>0.09283803013913394</v>
       </c>
       <c r="C19">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D19">
-        <v>0.11416146111309219</v>
+        <v>0.1141614676507628</v>
       </c>
       <c r="E19">
-        <v>0.11908212476580041</v>
+        <v>0.1190821320080275</v>
       </c>
       <c r="F19">
-        <v>0.116193810671591</v>
+        <v>0.1161938083426668</v>
       </c>
       <c r="G19">
-        <v>0.1190528825772484</v>
+        <v>0.1190528883284262</v>
       </c>
       <c r="H19">
-        <v>0.1043531550409718</v>
+        <v>0.1043531617818875</v>
       </c>
       <c r="I19">
-        <v>0.1005043452851338</v>
+        <v>0.1005043520988353</v>
       </c>
       <c r="J19">
-        <v>9.6122341517650214E-2</v>
+        <v>0.09612234664211425</v>
       </c>
       <c r="K19">
-        <v>9.061204782943906E-2</v>
+        <v>0.09061205172374731</v>
       </c>
       <c r="L19">
-        <v>8.6869815477270948E-2</v>
+        <v>0.08686982024356667</v>
       </c>
       <c r="M19">
-        <v>8.5630992762226549E-2</v>
+        <v>0.08563099534185399</v>
       </c>
       <c r="N19">
-        <v>8.384766365388642E-2</v>
+        <v>0.08384766597527363</v>
       </c>
       <c r="O19">
-        <v>8.3824924001451015E-2</v>
+        <v>0.08382492619679194</v>
       </c>
       <c r="P19">
-        <v>8.4639274584797641E-2</v>
+        <v>0.08463927702514666</v>
       </c>
       <c r="Q19">
-        <v>8.4411364799827221E-2</v>
+        <v>0.08441136673247797</v>
       </c>
       <c r="R19">
-        <v>8.5261045834951976E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>36</v>
+        <v>0.08526104561966302</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>9.4059910666150659E-2</v>
+        <v>0.09405991511715775</v>
       </c>
       <c r="C20">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D20">
-        <v>0.1138918688206946</v>
+        <v>0.1138918751955896</v>
       </c>
       <c r="E20">
-        <v>0.1194848873280899</v>
+        <v>0.1194848968834142</v>
       </c>
       <c r="F20">
-        <v>0.1175326821066953</v>
+        <v>0.1175326878210851</v>
       </c>
       <c r="G20">
-        <v>0.11257322762262501</v>
+        <v>0.1125732289309126</v>
       </c>
       <c r="H20">
-        <v>0.10617230775180191</v>
+        <v>0.1061723140068754</v>
       </c>
       <c r="I20">
-        <v>0.1038201102081415</v>
+        <v>0.1038201148966972</v>
       </c>
       <c r="J20">
-        <v>9.8172704485272919E-2</v>
+        <v>0.09817270868371006</v>
       </c>
       <c r="K20">
-        <v>9.2760252603511437E-2</v>
+        <v>0.09276025488296602</v>
       </c>
       <c r="L20">
-        <v>9.019151614406723E-2</v>
+        <v>0.09019151944497544</v>
       </c>
       <c r="M20">
-        <v>8.7034684204047669E-2</v>
+        <v>0.08703468635691143</v>
       </c>
       <c r="N20">
-        <v>8.6900104756157157E-2</v>
+        <v>0.08690010899378932</v>
       </c>
       <c r="O20">
-        <v>8.679184471868312E-2</v>
+        <v>0.08679184893394525</v>
       </c>
       <c r="P20">
-        <v>8.3665490232079753E-2</v>
+        <v>0.08366549229554014</v>
       </c>
       <c r="Q20">
-        <v>8.4066582604125417E-2</v>
+        <v>0.08406658253424083</v>
       </c>
       <c r="R20">
-        <v>8.4314471469758595E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>37</v>
+        <v>0.08431447144381471</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>0.10681128480111619</v>
+        <v>0.1068112884730779</v>
       </c>
       <c r="C21">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D21">
-        <v>0.1133179409072156</v>
+        <v>0.1133179471180445</v>
       </c>
       <c r="E21">
-        <v>0.1221362301155112</v>
+        <v>0.1221362402731554</v>
       </c>
       <c r="F21">
-        <v>0.11957356152538411</v>
+        <v>0.1195735668001651</v>
       </c>
       <c r="G21">
-        <v>0.11217911766094869</v>
+        <v>0.1121791301805793</v>
       </c>
       <c r="H21">
-        <v>0.10841733302979049</v>
+        <v>0.1084173391523654</v>
       </c>
       <c r="I21">
-        <v>0.1067297726325224</v>
+        <v>0.1067297787327727</v>
       </c>
       <c r="J21">
-        <v>0.1033335145108039</v>
+        <v>0.1033335170430377</v>
       </c>
       <c r="K21">
-        <v>0.1007058414236934</v>
+        <v>0.1007058448337699</v>
       </c>
       <c r="L21">
-        <v>9.592259173858754E-2</v>
+        <v>0.09592259207338709</v>
       </c>
       <c r="M21">
-        <v>9.3582510050331122E-2</v>
+        <v>0.09358250850484293</v>
       </c>
       <c r="N21">
-        <v>9.2573528363970661E-2</v>
+        <v>0.0925735231278591</v>
       </c>
       <c r="O21">
-        <v>9.3807238648662306E-2</v>
+        <v>0.0938072291938551</v>
       </c>
       <c r="P21">
-        <v>9.6665282767824046E-2</v>
+        <v>0.09666526755038206</v>
       </c>
       <c r="Q21">
-        <v>9.797305665911657E-2</v>
+        <v>0.09797303401673238</v>
       </c>
       <c r="R21">
-        <v>9.7002528682656436E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>38</v>
+        <v>0.09700250147772804</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>0.1098189736273104</v>
+        <v>0.1098189714506535</v>
       </c>
       <c r="C22">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D22">
-        <v>0.11306385667693521</v>
+        <v>0.1130638629358482</v>
       </c>
       <c r="E22">
-        <v>0.12139496331372179</v>
+        <v>0.1213949728630994</v>
       </c>
       <c r="F22">
-        <v>0.1189725029975888</v>
+        <v>0.1189725096646562</v>
       </c>
       <c r="G22">
-        <v>0.111596368163804</v>
+        <v>0.1115963770639219</v>
       </c>
       <c r="H22">
-        <v>0.10856415439800179</v>
+        <v>0.1085641612443949</v>
       </c>
       <c r="I22">
-        <v>0.1072029241612019</v>
+        <v>0.1072029274779717</v>
       </c>
       <c r="J22">
-        <v>0.1055350878211129</v>
+        <v>0.1055350944792129</v>
       </c>
       <c r="K22">
-        <v>0.1044902264703023</v>
+        <v>0.1044902241907652</v>
       </c>
       <c r="L22">
-        <v>9.9780702396864721E-2</v>
+        <v>0.0997807007968272</v>
       </c>
       <c r="M22">
-        <v>9.7340705137301961E-2</v>
+        <v>0.09734070178036053</v>
       </c>
       <c r="N22">
-        <v>9.6238576674606988E-2</v>
+        <v>0.09623857129683384</v>
       </c>
       <c r="O22">
-        <v>9.5703984121024904E-2</v>
+        <v>0.09570397282001189</v>
       </c>
       <c r="P22">
-        <v>9.682291778846977E-2</v>
+        <v>0.0968228987837912</v>
       </c>
       <c r="Q22">
-        <v>9.6911477202855423E-2</v>
+        <v>0.09691145269257632</v>
       </c>
       <c r="R22">
-        <v>9.690333797718699E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>39</v>
+        <v>0.09690330819568387</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>9.7784766900242237E-2</v>
+        <v>0.09778477445650534</v>
       </c>
       <c r="C23">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D23">
-        <v>0.11421377304206271</v>
+        <v>0.1142137794016392</v>
       </c>
       <c r="E23">
-        <v>0.12020297777402569</v>
+        <v>0.1202029825709711</v>
       </c>
       <c r="F23">
-        <v>0.1147223221649856</v>
+        <v>0.1147223311582795</v>
       </c>
       <c r="G23">
-        <v>0.1078905333112114</v>
+        <v>0.1078905383059911</v>
       </c>
       <c r="H23">
-        <v>9.9552098280713097E-2</v>
+        <v>0.09955210572526503</v>
       </c>
       <c r="I23">
-        <v>9.3452329973621878E-2</v>
+        <v>0.09345233683581988</v>
       </c>
       <c r="J23">
-        <v>9.1155080653853318E-2</v>
+        <v>0.09115508410265276</v>
       </c>
       <c r="K23">
-        <v>9.0272763382096388E-2</v>
+        <v>0.09027276402019509</v>
       </c>
       <c r="L23">
-        <v>8.8716447820740646E-2</v>
+        <v>0.08871644535509376</v>
       </c>
       <c r="M23">
-        <v>8.8859984517314E-2</v>
+        <v>0.08885997240070824</v>
       </c>
       <c r="N23">
-        <v>8.9490043477417666E-2</v>
+        <v>0.08949002515055565</v>
       </c>
       <c r="O23">
-        <v>9.0457707395776049E-2</v>
+        <v>0.09045768225538005</v>
       </c>
       <c r="P23">
-        <v>9.0788920260187755E-2</v>
+        <v>0.09078889343235633</v>
       </c>
       <c r="Q23">
-        <v>9.1021525082719407E-2</v>
+        <v>0.09102149601815752</v>
       </c>
       <c r="R23">
-        <v>9.2534571630234361E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>40</v>
+        <v>0.09253454792468935</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>0.1120037287055218</v>
+        <v>0.1120037320958052</v>
       </c>
       <c r="C24">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D24">
-        <v>0.1156299130288642</v>
+        <v>0.1156299190056313</v>
       </c>
       <c r="E24">
-        <v>0.1185210686286928</v>
+        <v>0.118521071329813</v>
       </c>
       <c r="F24">
-        <v>0.1213181533806123</v>
+        <v>0.1213181601343831</v>
       </c>
       <c r="G24">
-        <v>0.1194497201570958</v>
+        <v>0.1194497224646666</v>
       </c>
       <c r="H24">
-        <v>0.11839305233688981</v>
+        <v>0.1183930530346823</v>
       </c>
       <c r="I24">
-        <v>0.1155106004368</v>
+        <v>0.1155106057682321</v>
       </c>
       <c r="J24">
-        <v>0.1181432614427437</v>
+        <v>0.1181432684357682</v>
       </c>
       <c r="K24">
-        <v>0.1152451168918711</v>
+        <v>0.1152451222733793</v>
       </c>
       <c r="L24">
-        <v>0.1066834724738964</v>
+        <v>0.1066834746847534</v>
       </c>
       <c r="M24">
-        <v>0.1005366133481493</v>
+        <v>0.1005366136990388</v>
       </c>
       <c r="N24">
-        <v>9.8415810672204812E-2</v>
+        <v>0.0984158074858716</v>
       </c>
       <c r="O24">
-        <v>9.9961078616776347E-2</v>
+        <v>0.09996106737132282</v>
       </c>
       <c r="P24">
-        <v>0.1037918294822175</v>
+        <v>0.1037918115799672</v>
       </c>
       <c r="Q24">
-        <v>0.1074967551493432</v>
+        <v>0.1074967336709198</v>
       </c>
       <c r="R24">
-        <v>0.11214276710093871</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>41</v>
+        <v>0.1121427403054605</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>0.1136247487700115</v>
+        <v>0.1136247516830104</v>
       </c>
       <c r="C25">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D25">
-        <v>0.11574599850638841</v>
+        <v>0.1157460050585653</v>
       </c>
       <c r="E25">
-        <v>0.1188425868344105</v>
+        <v>0.1188425901125708</v>
       </c>
       <c r="F25">
-        <v>0.12193276600167691</v>
+        <v>0.1219327726055044</v>
       </c>
       <c r="G25">
-        <v>0.1195765909148228</v>
+        <v>0.1195765979076372</v>
       </c>
       <c r="H25">
-        <v>0.1180867262221795</v>
+        <v>0.1180867299303622</v>
       </c>
       <c r="I25">
-        <v>0.11766382345992769</v>
+        <v>0.1176638292859434</v>
       </c>
       <c r="J25">
-        <v>0.12269207084804611</v>
+        <v>0.1226920756456702</v>
       </c>
       <c r="K25">
-        <v>0.11906210468748959</v>
+        <v>0.1190621062127353</v>
       </c>
       <c r="L25">
-        <v>0.11472850814991151</v>
+        <v>0.1147285102728625</v>
       </c>
       <c r="M25">
-        <v>0.10298828861822509</v>
+        <v>0.1029882891713844</v>
       </c>
       <c r="N25">
-        <v>0.101249788402823</v>
+        <v>0.101249788028136</v>
       </c>
       <c r="O25">
-        <v>0.100289142524247</v>
+        <v>0.1002891362652923</v>
       </c>
       <c r="P25">
-        <v>0.1021439448808393</v>
+        <v>0.102143932343885</v>
       </c>
       <c r="Q25">
-        <v>0.1052314257486494</v>
+        <v>0.1052314064710939</v>
       </c>
       <c r="R25">
-        <v>0.1094423836787002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>42</v>
+        <v>0.1094423611534655</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>0.11550356835000999</v>
+        <v>0.1155035713895744</v>
       </c>
       <c r="C26">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D26">
-        <v>0.1157883488612346</v>
+        <v>0.1157883549184937</v>
       </c>
       <c r="E26">
-        <v>0.1194401290507603</v>
+        <v>0.119440133262905</v>
       </c>
       <c r="F26">
-        <v>0.1199892187713784</v>
+        <v>0.1199892252755396</v>
       </c>
       <c r="G26">
-        <v>0.1170122946184502</v>
+        <v>0.117012302919752</v>
       </c>
       <c r="H26">
-        <v>0.1192303528367756</v>
+        <v>0.119230357685926</v>
       </c>
       <c r="I26">
-        <v>0.1171508692285349</v>
+        <v>0.1171508760772795</v>
       </c>
       <c r="J26">
-        <v>0.1110211983550507</v>
+        <v>0.1110212030616426</v>
       </c>
       <c r="K26">
-        <v>0.1144978473096112</v>
+        <v>0.1144978519561233</v>
       </c>
       <c r="L26">
-        <v>0.10675445274937879</v>
+        <v>0.106754447816608</v>
       </c>
       <c r="M26">
-        <v>0.1017406557852702</v>
+        <v>0.1017406572654887</v>
       </c>
       <c r="N26">
-        <v>0.1010059098984236</v>
+        <v>0.1010059084367485</v>
       </c>
       <c r="O26">
-        <v>0.1023296362557672</v>
+        <v>0.1023296274255464</v>
       </c>
       <c r="P26">
-        <v>0.10440055858575011</v>
+        <v>0.1044005445832904</v>
       </c>
       <c r="Q26">
-        <v>0.1081457070829724</v>
+        <v>0.108145687107509</v>
       </c>
       <c r="R26">
-        <v>0.1130621422524668</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>43</v>
+        <v>0.1130621179693679</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>0.1039745010901134</v>
+        <v>0.1039745036888077</v>
       </c>
       <c r="C27">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D27">
-        <v>0.1157015766663142</v>
+        <v>0.1157015829984323</v>
       </c>
       <c r="E27">
-        <v>0.11855541300790171</v>
+        <v>0.1185554171217785</v>
       </c>
       <c r="F27">
-        <v>0.1191216854851618</v>
+        <v>0.1191216929854225</v>
       </c>
       <c r="G27">
-        <v>0.1160123961867186</v>
+        <v>0.1160124010469104</v>
       </c>
       <c r="H27">
-        <v>0.1178639662467065</v>
+        <v>0.117863970287782</v>
       </c>
       <c r="I27">
-        <v>0.1161678716923978</v>
+        <v>0.1161678779930079</v>
       </c>
       <c r="J27">
-        <v>0.1110615726347299</v>
+        <v>0.1110615775999367</v>
       </c>
       <c r="K27">
-        <v>0.1138460491878146</v>
+        <v>0.1138460529568381</v>
       </c>
       <c r="L27">
-        <v>0.10790698159204699</v>
+        <v>0.1079069866460022</v>
       </c>
       <c r="M27">
-        <v>0.1002438923885586</v>
+        <v>0.1002438950602269</v>
       </c>
       <c r="N27">
-        <v>9.6280774290876614E-2</v>
+        <v>0.09628077592686604</v>
       </c>
       <c r="O27">
-        <v>9.5063480877237358E-2</v>
+        <v>0.09506347874950921</v>
       </c>
       <c r="P27">
-        <v>9.3603590012935722E-2</v>
+        <v>0.09360358684599662</v>
       </c>
       <c r="Q27">
-        <v>9.5296650686734527E-2</v>
+        <v>0.09529664610275786</v>
       </c>
       <c r="R27">
-        <v>9.5884130366224257E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>44</v>
+        <v>0.09588412545567743</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>0.10704616293446979</v>
+        <v>0.1070461666490651</v>
       </c>
       <c r="C28">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D28">
-        <v>0.1156704472555639</v>
+        <v>0.1156704532007953</v>
       </c>
       <c r="E28">
-        <v>0.118475134397202</v>
+        <v>0.1184751377514689</v>
       </c>
       <c r="F28">
-        <v>0.12136696924998271</v>
+        <v>0.1213669758431148</v>
       </c>
       <c r="G28">
-        <v>0.11907242414581699</v>
+        <v>0.1190724304517015</v>
       </c>
       <c r="H28">
-        <v>0.11791541258812011</v>
+        <v>0.1179154181012933</v>
       </c>
       <c r="I28">
-        <v>0.11707673716810239</v>
+        <v>0.1170767448959439</v>
       </c>
       <c r="J28">
-        <v>0.1204800415865477</v>
+        <v>0.1204800466564626</v>
       </c>
       <c r="K28">
-        <v>0.1195772565581625</v>
+        <v>0.1195772624605623</v>
       </c>
       <c r="L28">
-        <v>0.11593674072132069</v>
+        <v>0.1159367466479789</v>
       </c>
       <c r="M28">
-        <v>0.10293187172251431</v>
+        <v>0.1029318740508096</v>
       </c>
       <c r="N28">
-        <v>0.10016857285287779</v>
+        <v>0.100168574315961</v>
       </c>
       <c r="O28">
-        <v>9.8021361926867473E-2</v>
+        <v>0.09802136225545413</v>
       </c>
       <c r="P28">
-        <v>9.7330291189149473E-2</v>
+        <v>0.0973302910058538</v>
       </c>
       <c r="Q28">
-        <v>9.699409373809928E-2</v>
+        <v>0.09699409228779055</v>
       </c>
       <c r="R28">
-        <v>9.7068939503392362E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>45</v>
+        <v>0.09706893579760224</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>0.10344593555754091</v>
+        <v>0.103445937288252</v>
       </c>
       <c r="C29">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D29">
-        <v>0.1157487843777921</v>
+        <v>0.1157487911904185</v>
       </c>
       <c r="E29">
-        <v>0.1188815068264524</v>
+        <v>0.1188815107275639</v>
       </c>
       <c r="F29">
-        <v>0.1217492530254338</v>
+        <v>0.121749259346964</v>
       </c>
       <c r="G29">
-        <v>0.11930985877803869</v>
+        <v>0.119309858946695</v>
       </c>
       <c r="H29">
-        <v>0.1179508476782004</v>
+        <v>0.117950845472246</v>
       </c>
       <c r="I29">
-        <v>0.1167681758508816</v>
+        <v>0.1167681817263092</v>
       </c>
       <c r="J29">
-        <v>0.1200610860075262</v>
+        <v>0.1200610906440986</v>
       </c>
       <c r="K29">
-        <v>0.1184049718464084</v>
+        <v>0.1184049768681853</v>
       </c>
       <c r="L29">
-        <v>0.115413058722763</v>
+        <v>0.1154130606854456</v>
       </c>
       <c r="M29">
-        <v>0.1029236079239686</v>
+        <v>0.1029236105165915</v>
       </c>
       <c r="N29">
-        <v>9.9864882885764894E-2</v>
+        <v>0.09986488450410869</v>
       </c>
       <c r="O29">
-        <v>9.7480283515426577E-2</v>
+        <v>0.09748028432454856</v>
       </c>
       <c r="P29">
-        <v>9.6612135799176435E-2</v>
+        <v>0.0966121364829564</v>
       </c>
       <c r="Q29">
-        <v>9.5752665791023761E-2</v>
+        <v>0.09575266356747249</v>
       </c>
       <c r="R29">
-        <v>9.5740109057876985E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>46</v>
+        <v>0.09574010561392124</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>0.1058410623941359</v>
+        <v>0.1058410641179377</v>
       </c>
       <c r="C30">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D30">
-        <v>0.11578220531429639</v>
+        <v>0.1157822116972108</v>
       </c>
       <c r="E30">
-        <v>0.1187646629525992</v>
+        <v>0.1187646669529951</v>
       </c>
       <c r="F30">
-        <v>0.1215362419045433</v>
+        <v>0.1215362483057885</v>
       </c>
       <c r="G30">
-        <v>0.119262979862404</v>
+        <v>0.1192629873424644</v>
       </c>
       <c r="H30">
-        <v>0.1183151174919061</v>
+        <v>0.1183151226405939</v>
       </c>
       <c r="I30">
-        <v>0.1173059803822005</v>
+        <v>0.1173059862727679</v>
       </c>
       <c r="J30">
-        <v>0.12046040910388429</v>
+        <v>0.120460415063399</v>
       </c>
       <c r="K30">
-        <v>0.1191774717370066</v>
+        <v>0.1191774769052874</v>
       </c>
       <c r="L30">
-        <v>0.1161978059338734</v>
+        <v>0.116197810714407</v>
       </c>
       <c r="M30">
-        <v>0.10413484861780641</v>
+        <v>0.1041348509832463</v>
       </c>
       <c r="N30">
-        <v>0.10084168365648299</v>
+        <v>0.1008416852231193</v>
       </c>
       <c r="O30">
-        <v>9.8837636292215258E-2</v>
+        <v>0.09883763623032359</v>
       </c>
       <c r="P30">
-        <v>9.708076569976884E-2</v>
+        <v>0.09708076624592016</v>
       </c>
       <c r="Q30">
-        <v>9.608832253961784E-2</v>
+        <v>0.09608832049585303</v>
       </c>
       <c r="R30">
-        <v>9.5392618476584534E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>47</v>
+        <v>0.09539261488586902</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>0.10764062632783571</v>
+        <v>0.1076406287994534</v>
       </c>
       <c r="C31">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D31">
-        <v>0.11574601530416841</v>
+        <v>0.1157460221164351</v>
       </c>
       <c r="E31">
-        <v>0.1184664611999707</v>
+        <v>0.1184664647177015</v>
       </c>
       <c r="F31">
-        <v>0.1213504526876422</v>
+        <v>0.1213504698579847</v>
       </c>
       <c r="G31">
-        <v>0.1190330682582898</v>
+        <v>0.1190330749967072</v>
       </c>
       <c r="H31">
-        <v>0.1179588611380927</v>
+        <v>0.1179588671961681</v>
       </c>
       <c r="I31">
-        <v>0.1169260593078973</v>
+        <v>0.1169260652286189</v>
       </c>
       <c r="J31">
-        <v>0.120506901707421</v>
+        <v>0.1205069067940936</v>
       </c>
       <c r="K31">
-        <v>0.11898782571530619</v>
+        <v>0.1189878298101055</v>
       </c>
       <c r="L31">
-        <v>0.11642491446593391</v>
+        <v>0.1164249151067983</v>
       </c>
       <c r="M31">
-        <v>0.1056803874012063</v>
+        <v>0.1056803897762556</v>
       </c>
       <c r="N31">
-        <v>0.101839574151964</v>
+        <v>0.1018395761265171</v>
       </c>
       <c r="O31">
-        <v>9.9581862880923785E-2</v>
+        <v>0.09958186350608524</v>
       </c>
       <c r="P31">
-        <v>9.7782390622230236E-2</v>
+        <v>0.09778239529742452</v>
       </c>
       <c r="Q31">
-        <v>9.6626166636540015E-2</v>
+        <v>0.09662616789649926</v>
       </c>
       <c r="R31">
-        <v>9.4905561950673914E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>48</v>
+        <v>0.09490556225914228</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>0.1091826531990161</v>
+        <v>0.1091826553665487</v>
       </c>
       <c r="C32">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D32">
-        <v>0.11562784727953559</v>
+        <v>0.1156278532805013</v>
       </c>
       <c r="E32">
-        <v>0.1187639497604701</v>
+        <v>0.1187639520122758</v>
       </c>
       <c r="F32">
-        <v>0.12165419133366551</v>
+        <v>0.1216541988306914</v>
       </c>
       <c r="G32">
-        <v>0.1195121721521834</v>
+        <v>0.1195121751848061</v>
       </c>
       <c r="H32">
-        <v>0.1180794892049175</v>
+        <v>0.1180794929407197</v>
       </c>
       <c r="I32">
-        <v>0.1171008146898924</v>
+        <v>0.1171008188890086</v>
       </c>
       <c r="J32">
-        <v>0.1208578613739533</v>
+        <v>0.1208578669144584</v>
       </c>
       <c r="K32">
-        <v>0.118862369252502</v>
+        <v>0.1188623747036195</v>
       </c>
       <c r="L32">
-        <v>0.11569921663536629</v>
+        <v>0.1156992212417473</v>
       </c>
       <c r="M32">
-        <v>0.10325756263202369</v>
+        <v>0.1032575645612177</v>
       </c>
       <c r="N32">
-        <v>0.10009006544157829</v>
+        <v>0.1000900663172228</v>
       </c>
       <c r="O32">
-        <v>9.8425591057009654E-2</v>
+        <v>0.09842559058808531</v>
       </c>
       <c r="P32">
-        <v>9.8317445040527418E-2</v>
+        <v>0.09831744217971809</v>
       </c>
       <c r="Q32">
-        <v>9.9480949122511861E-2</v>
+        <v>0.09948094379783841</v>
       </c>
       <c r="R32">
-        <v>0.1007796734250155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>49</v>
+        <v>0.1007796650087474</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>0.1073670217604366</v>
+        <v>0.1073670244951569</v>
       </c>
       <c r="C33">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D33">
-        <v>0.11559206565918689</v>
+        <v>0.1155920716719309</v>
       </c>
       <c r="E33">
-        <v>0.11849160505436671</v>
+        <v>0.118491608407732</v>
       </c>
       <c r="F33">
-        <v>0.12133534038965541</v>
+        <v>0.1213353473073744</v>
       </c>
       <c r="G33">
-        <v>0.11890529695740359</v>
+        <v>0.1189053009516235</v>
       </c>
       <c r="H33">
-        <v>0.11770197591949939</v>
+        <v>0.1177019789772663</v>
       </c>
       <c r="I33">
-        <v>0.11672020984203491</v>
+        <v>0.1167202153675209</v>
       </c>
       <c r="J33">
-        <v>0.1206699728505682</v>
+        <v>0.1206699793817465</v>
       </c>
       <c r="K33">
-        <v>0.11858062488892231</v>
+        <v>0.1185806302801819</v>
       </c>
       <c r="L33">
-        <v>0.11522676077471949</v>
+        <v>0.1152267676689464</v>
       </c>
       <c r="M33">
-        <v>0.10292513497833231</v>
+        <v>0.102925137229959</v>
       </c>
       <c r="N33">
-        <v>0.1003144140203629</v>
+        <v>0.1003144157155404</v>
       </c>
       <c r="O33">
-        <v>9.8221061766306544E-2</v>
+        <v>0.09822106176808891</v>
       </c>
       <c r="P33">
-        <v>9.7792960062385928E-2</v>
+        <v>0.0977929600674366</v>
       </c>
       <c r="Q33">
-        <v>9.8190093847988338E-2</v>
+        <v>0.09819009129104884</v>
       </c>
       <c r="R33">
-        <v>9.9082423864482863E-2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>50</v>
+        <v>0.09908241806933997</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>0.1078521762026317</v>
+        <v>0.1078521780067554</v>
       </c>
       <c r="C34">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D34">
-        <v>0.1155450518586061</v>
+        <v>0.1155450579207682</v>
       </c>
       <c r="E34">
-        <v>0.1186604562318522</v>
+        <v>0.1186604597182626</v>
       </c>
       <c r="F34">
-        <v>0.1215475704272104</v>
+        <v>0.121547577202441</v>
       </c>
       <c r="G34">
-        <v>0.1194873498422771</v>
+        <v>0.1194873543655426</v>
       </c>
       <c r="H34">
-        <v>0.11816224472390729</v>
+        <v>0.1181622498686636</v>
       </c>
       <c r="I34">
-        <v>0.1171730372658044</v>
+        <v>0.1171730431895672</v>
       </c>
       <c r="J34">
-        <v>0.12052087021540379</v>
+        <v>0.120520875636432</v>
       </c>
       <c r="K34">
-        <v>0.1194590809062364</v>
+        <v>0.119459086038548</v>
       </c>
       <c r="L34">
-        <v>0.116133579354344</v>
+        <v>0.116133584120626</v>
       </c>
       <c r="M34">
-        <v>0.10408189426601509</v>
+        <v>0.1040818961995446</v>
       </c>
       <c r="N34">
-        <v>0.1006957230259381</v>
+        <v>0.1006957242350456</v>
       </c>
       <c r="O34">
-        <v>9.881183121716719E-2</v>
+        <v>0.09881183154166159</v>
       </c>
       <c r="P34">
-        <v>9.8030110815300539E-2</v>
+        <v>0.09803011012976443</v>
       </c>
       <c r="Q34">
-        <v>9.8356825790067604E-2</v>
+        <v>0.09835682276740781</v>
       </c>
       <c r="R34">
-        <v>9.9062624830105125E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>51</v>
+        <v>0.09906262087163699</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>0.10918495610233001</v>
+        <v>0.1091849584817027</v>
       </c>
       <c r="C35">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D35">
-        <v>0.115861218537987</v>
+        <v>0.1158612250652068</v>
       </c>
       <c r="E35">
-        <v>0.11920537437493391</v>
+        <v>0.1192053778385412</v>
       </c>
       <c r="F35">
-        <v>0.1219291639054421</v>
+        <v>0.1219291709806561</v>
       </c>
       <c r="G35">
-        <v>0.1196630440321973</v>
+        <v>0.1196630494192905</v>
       </c>
       <c r="H35">
-        <v>0.11851610528471861</v>
+        <v>0.1185161113431146</v>
       </c>
       <c r="I35">
-        <v>0.1176731384353801</v>
+        <v>0.1176731443916701</v>
       </c>
       <c r="J35">
-        <v>0.12117861895950829</v>
+        <v>0.1211786242367391</v>
       </c>
       <c r="K35">
-        <v>0.1197554790998957</v>
+        <v>0.1197554847076231</v>
       </c>
       <c r="L35">
-        <v>0.1164652311656228</v>
+        <v>0.1164652351365039</v>
       </c>
       <c r="M35">
-        <v>0.104542462535094</v>
+        <v>0.1045424650539163</v>
       </c>
       <c r="N35">
-        <v>0.101819735745033</v>
+        <v>0.1018197372182899</v>
       </c>
       <c r="O35">
-        <v>9.9425717576739611E-2</v>
+        <v>0.09942571855316713</v>
       </c>
       <c r="P35">
-        <v>9.8250189025975709E-2</v>
+        <v>0.09825018921649209</v>
       </c>
       <c r="Q35">
-        <v>9.8241503402269739E-2</v>
+        <v>0.0982415018515379</v>
       </c>
       <c r="R35">
-        <v>9.8405077946614433E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>52</v>
+        <v>0.09840507447494296</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>0.1073422484093875</v>
+        <v>0.1073422504483583</v>
       </c>
       <c r="C36">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D36">
-        <v>0.1155701518227038</v>
+        <v>0.1155701580416752</v>
       </c>
       <c r="E36">
-        <v>0.11876784760425491</v>
+        <v>0.1187678514965555</v>
       </c>
       <c r="F36">
-        <v>0.1215309924248964</v>
+        <v>0.1215309994562407</v>
       </c>
       <c r="G36">
-        <v>0.1189650954611452</v>
+        <v>0.1189651021063094</v>
       </c>
       <c r="H36">
-        <v>0.1179263342433271</v>
+        <v>0.1179263373753756</v>
       </c>
       <c r="I36">
-        <v>0.1169456640398952</v>
+        <v>0.1169456677364436</v>
       </c>
       <c r="J36">
-        <v>0.1194340192194757</v>
+        <v>0.1194340249972129</v>
       </c>
       <c r="K36">
-        <v>0.11830079365589841</v>
+        <v>0.1183007987570422</v>
       </c>
       <c r="L36">
-        <v>0.1154297572180001</v>
+        <v>0.1154297617203766</v>
       </c>
       <c r="M36">
-        <v>0.1061359646468301</v>
+        <v>0.106135966900142</v>
       </c>
       <c r="N36">
-        <v>0.1016834090556195</v>
+        <v>0.1016834101101453</v>
       </c>
       <c r="O36">
-        <v>9.9564548317472051E-2</v>
+        <v>0.09956454895547123</v>
       </c>
       <c r="P36">
-        <v>9.7591029664163512E-2</v>
+        <v>0.09759103080465244</v>
       </c>
       <c r="Q36">
-        <v>9.7195689862874177E-2</v>
+        <v>0.09719569014324206</v>
       </c>
       <c r="R36">
-        <v>9.5453053430557752E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>53</v>
+        <v>0.09545305139567106</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>0.11874584982919199</v>
+        <v>0.1187458535811828</v>
       </c>
       <c r="C37">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D37">
-        <v>0.1180998203677147</v>
+        <v>0.1180998247857414</v>
       </c>
       <c r="E37">
-        <v>0.1218185327700569</v>
+        <v>0.1218185367975501</v>
       </c>
       <c r="F37">
-        <v>0.1180895496682618</v>
+        <v>0.1180895554014565</v>
       </c>
       <c r="G37">
-        <v>0.11338390202449759</v>
+        <v>0.1133839106700547</v>
       </c>
       <c r="H37">
-        <v>0.1163654024631568</v>
+        <v>0.1163654068579704</v>
       </c>
       <c r="I37">
-        <v>0.1133721756848899</v>
+        <v>0.1133721779305426</v>
       </c>
       <c r="J37">
-        <v>0.1079054103956656</v>
+        <v>0.1079054036331593</v>
       </c>
       <c r="K37">
-        <v>0.1059954594155231</v>
+        <v>0.1059954496844027</v>
       </c>
       <c r="L37">
-        <v>0.1065469897686574</v>
+        <v>0.1065469810760124</v>
       </c>
       <c r="M37">
-        <v>0.10629124404523831</v>
+        <v>0.106291232622946</v>
       </c>
       <c r="N37">
-        <v>0.1071211947346707</v>
+        <v>0.1071211797487109</v>
       </c>
       <c r="O37">
-        <v>0.1095542780723316</v>
+        <v>0.1095542611902365</v>
       </c>
       <c r="P37">
-        <v>0.1079460829827114</v>
+        <v>0.1079460552644229</v>
       </c>
       <c r="Q37">
-        <v>0.1077413216741919</v>
+        <v>0.1077412802087406</v>
       </c>
       <c r="R37">
-        <v>0.10757307702002419</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>54</v>
+        <v>0.1075730214594462</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>0.1045468994066972</v>
+        <v>0.1045469032079323</v>
       </c>
       <c r="C38">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D38">
-        <v>0.11682464697425091</v>
+        <v>0.1168246519124035</v>
       </c>
       <c r="E38">
-        <v>0.1211396444439799</v>
+        <v>0.1211396509826052</v>
       </c>
       <c r="F38">
-        <v>0.11978531949004689</v>
+        <v>0.1197853376253491</v>
       </c>
       <c r="G38">
-        <v>0.1125394688138763</v>
+        <v>0.1125394745206883</v>
       </c>
       <c r="H38">
-        <v>0.1112956264427621</v>
+        <v>0.1112956328359029</v>
       </c>
       <c r="I38">
-        <v>0.10350749646090041</v>
+        <v>0.1035075016717224</v>
       </c>
       <c r="J38">
-        <v>9.5120795828348093E-2</v>
+        <v>0.09512079547959258</v>
       </c>
       <c r="K38">
-        <v>9.574871728724535E-2</v>
+        <v>0.09574875355810682</v>
       </c>
       <c r="L38">
-        <v>9.8524076392877441E-2</v>
+        <v>0.09852407420211431</v>
       </c>
       <c r="M38">
-        <v>0.1011461839963268</v>
+        <v>0.1011461781471454</v>
       </c>
       <c r="N38">
-        <v>0.1011190930167289</v>
+        <v>0.1011190846546421</v>
       </c>
       <c r="O38">
-        <v>0.102221307964761</v>
+        <v>0.1022213016394909</v>
       </c>
       <c r="P38">
-        <v>0.10213942751981681</v>
+        <v>0.1021394238653954</v>
       </c>
       <c r="Q38">
-        <v>0.1010159945529102</v>
+        <v>0.1010159861616764</v>
       </c>
       <c r="R38">
-        <v>0.10015737039480729</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>55</v>
+        <v>0.1001573586087447</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>0.1059475728613256</v>
+        <v>0.1059475788561753</v>
       </c>
       <c r="C39">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D39">
-        <v>0.1165182733645697</v>
+        <v>0.1165182779921872</v>
       </c>
       <c r="E39">
-        <v>0.12003336752744601</v>
+        <v>0.120033372474991</v>
       </c>
       <c r="F39">
-        <v>0.1182994571576107</v>
+        <v>0.1182994715892043</v>
       </c>
       <c r="G39">
-        <v>0.1115216733359085</v>
+        <v>0.1115216748689022</v>
       </c>
       <c r="H39">
-        <v>0.1107555241426742</v>
+        <v>0.1107555232671681</v>
       </c>
       <c r="I39">
-        <v>0.1047594519980676</v>
+        <v>0.1047594566399006</v>
       </c>
       <c r="J39">
-        <v>9.7240620973479464E-2</v>
+        <v>0.09724062669429459</v>
       </c>
       <c r="K39">
-        <v>9.7745520395281699E-2</v>
+        <v>0.09774552648820024</v>
       </c>
       <c r="L39">
-        <v>9.6894575988092979E-2</v>
+        <v>0.09689457060985891</v>
       </c>
       <c r="M39">
-        <v>9.7826663458370142E-2</v>
+        <v>0.0978266604684217</v>
       </c>
       <c r="N39">
-        <v>9.8769935805948575E-2</v>
+        <v>0.09876993039877498</v>
       </c>
       <c r="O39">
-        <v>9.7608692926869883E-2</v>
+        <v>0.09760868545650511</v>
       </c>
       <c r="P39">
-        <v>9.8473837691948771E-2</v>
+        <v>0.09847382924094344</v>
       </c>
       <c r="Q39">
-        <v>9.9195904475717175E-2</v>
+        <v>0.09919589227180957</v>
       </c>
       <c r="R39">
-        <v>9.9116344157107364E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>56</v>
+        <v>0.09911632905534179</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>0.1160818412173031</v>
+        <v>0.1160818441516648</v>
       </c>
       <c r="C40">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D40">
-        <v>0.1182777290998735</v>
+        <v>0.118277733874746</v>
       </c>
       <c r="E40">
-        <v>0.11642068427728119</v>
+        <v>0.1164206887673199</v>
       </c>
       <c r="F40">
-        <v>0.1121412573750228</v>
+        <v>0.1121412640802488</v>
       </c>
       <c r="G40">
-        <v>0.11374668563691261</v>
+        <v>0.1137466913944166</v>
       </c>
       <c r="H40">
-        <v>0.10669928594999779</v>
+        <v>0.106699288488187</v>
       </c>
       <c r="I40">
-        <v>0.102815419366855</v>
+        <v>0.1028154209057984</v>
       </c>
       <c r="J40">
-        <v>0.10287292521671659</v>
+        <v>0.1028729224052054</v>
       </c>
       <c r="K40">
-        <v>0.10537708314522649</v>
+        <v>0.1053770752406959</v>
       </c>
       <c r="L40">
-        <v>0.10569314450267971</v>
+        <v>0.1056931342003427</v>
       </c>
       <c r="M40">
-        <v>0.1035304458495977</v>
+        <v>0.103530434130368</v>
       </c>
       <c r="N40">
-        <v>0.1038627399950014</v>
+        <v>0.1038627287350502</v>
       </c>
       <c r="O40">
-        <v>0.10259564760017729</v>
+        <v>0.1025956333974325</v>
       </c>
       <c r="P40">
-        <v>0.1036434102079971</v>
+        <v>0.103643386514851</v>
       </c>
       <c r="Q40">
-        <v>0.1055107194672246</v>
+        <v>0.1055106872765905</v>
       </c>
       <c r="R40">
-        <v>0.1091213725746033</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>57</v>
+        <v>0.1091213304394659</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>0.1189648475640671</v>
+        <v>0.118964856012883</v>
       </c>
       <c r="C41">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D41">
-        <v>0.1186398046841097</v>
+        <v>0.118639812908108</v>
       </c>
       <c r="E41">
-        <v>0.12663773178560431</v>
+        <v>0.1266377372297116</v>
       </c>
       <c r="F41">
-        <v>0.122061768227312</v>
+        <v>0.1220617741698206</v>
       </c>
       <c r="G41">
-        <v>0.12188529373600659</v>
+        <v>0.1218852991919377</v>
       </c>
       <c r="H41">
-        <v>0.11795136133670769</v>
+        <v>0.117951367158503</v>
       </c>
       <c r="I41">
-        <v>0.1168305099499122</v>
+        <v>0.1168305138245254</v>
       </c>
       <c r="J41">
-        <v>0.11557684124793791</v>
+        <v>0.1155768455543258</v>
       </c>
       <c r="K41">
-        <v>0.1129252831884477</v>
+        <v>0.1129252868157395</v>
       </c>
       <c r="L41">
-        <v>0.1145314880787506</v>
+        <v>0.1145314934976568</v>
       </c>
       <c r="M41">
-        <v>0.1164885176886227</v>
+        <v>0.1164885147489886</v>
       </c>
       <c r="N41">
-        <v>0.1158996171742827</v>
+        <v>0.1158996141951031</v>
       </c>
       <c r="O41">
-        <v>0.1171461646481182</v>
+        <v>0.1171461567831024</v>
       </c>
       <c r="P41">
-        <v>0.1202864548120101</v>
+        <v>0.1202864462144428</v>
       </c>
       <c r="Q41">
-        <v>0.12075342129772609</v>
+        <v>0.1207534123622056</v>
       </c>
       <c r="R41">
-        <v>0.1216011307785821</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>58</v>
+        <v>0.1216011201206001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>0.1062366615481535</v>
+        <v>0.1062366656695258</v>
       </c>
       <c r="C42">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D42">
-        <v>0.1132124591506475</v>
+        <v>0.1132124653307874</v>
       </c>
       <c r="E42">
-        <v>0.12815299344748621</v>
+        <v>0.1281530035399778</v>
       </c>
       <c r="F42">
-        <v>0.1214965789600272</v>
+        <v>0.1214965873969271</v>
       </c>
       <c r="G42">
-        <v>0.1089930373807806</v>
+        <v>0.1089930401796532</v>
       </c>
       <c r="H42">
-        <v>0.1046151214718062</v>
+        <v>0.1046151270682062</v>
       </c>
       <c r="I42">
-        <v>0.10217693768455691</v>
+        <v>0.1021769411179902</v>
       </c>
       <c r="J42">
-        <v>9.6820866566854777E-2</v>
+        <v>0.09682086974323596</v>
       </c>
       <c r="K42">
-        <v>9.5970188345315524E-2</v>
+        <v>0.09597019158358128</v>
       </c>
       <c r="L42">
-        <v>9.73913829136792E-2</v>
+        <v>0.09739138436301571</v>
       </c>
       <c r="M42">
-        <v>9.5670865510631031E-2</v>
+        <v>0.09567086200205353</v>
       </c>
       <c r="N42">
-        <v>9.5744165175891266E-2</v>
+        <v>0.09574416278517935</v>
       </c>
       <c r="O42">
-        <v>9.7174392131522486E-2</v>
+        <v>0.09717438680143196</v>
       </c>
       <c r="P42">
-        <v>9.7747492216740187E-2</v>
+        <v>0.0977474847688319</v>
       </c>
       <c r="Q42">
-        <v>9.7690577180186144E-2</v>
+        <v>0.09769056752357144</v>
       </c>
       <c r="R42">
-        <v>9.8535503671707464E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>59</v>
+        <v>0.09853549240692218</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>0.105558527019604</v>
+        <v>0.1055585355671282</v>
       </c>
       <c r="C43">
-        <v>0.11298752717561721</v>
+        <v>0.1129875329228996</v>
       </c>
       <c r="D43">
-        <v>0.11562436489869871</v>
+        <v>0.1156243729969769</v>
       </c>
       <c r="E43">
-        <v>0.1180865616861701</v>
+        <v>0.1180865678694039</v>
       </c>
       <c r="F43">
-        <v>0.11340538782522459</v>
+        <v>0.1134053937210262</v>
       </c>
       <c r="G43">
-        <v>0.11094603464175069</v>
+        <v>0.1109460418971855</v>
       </c>
       <c r="H43">
-        <v>0.10183228737346491</v>
+        <v>0.1018322915936524</v>
       </c>
       <c r="I43">
-        <v>9.8695258547852563E-2</v>
+        <v>0.09869526766602514</v>
       </c>
       <c r="J43">
-        <v>9.6712560477649798E-2</v>
+        <v>0.09671256563953874</v>
       </c>
       <c r="K43">
-        <v>9.7820964736921812E-2</v>
+        <v>0.09782096850889242</v>
       </c>
       <c r="L43">
-        <v>0.1002037971922513</v>
+        <v>0.1002038003187087</v>
       </c>
       <c r="M43">
-        <v>9.7393899008806489E-2</v>
+        <v>0.09739390110914554</v>
       </c>
       <c r="N43">
-        <v>9.6914386338298159E-2</v>
+        <v>0.09691439018376975</v>
       </c>
       <c r="O43">
-        <v>9.6484386208275555E-2</v>
+        <v>0.09648437838918306</v>
       </c>
       <c r="P43">
-        <v>9.7894118480025383E-2</v>
+        <v>0.09789413467000979</v>
       </c>
       <c r="Q43">
-        <v>9.9234606512678417E-2</v>
+        <v>0.09923462323048762</v>
       </c>
       <c r="R43">
-        <v>0.1002665188046679</v>
+        <v>0.1002665137954798</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:R43">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>